--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -915,7 +915,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -928,18 +928,21 @@
         <v>waveGap</v>
       </c>
       <c r="D1" t="str">
+        <v>dropGroup</v>
+      </c>
+      <c r="E1" t="str">
         <v>waveIndex</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>type</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>count</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>interval</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>hp</v>
       </c>
     </row>
@@ -953,19 +956,22 @@
       <c r="C2">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" t="str">
+      <c r="D2" t="str">
+        <v>level_1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
         <v>zombie</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>6</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.7</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v/>
       </c>
     </row>
@@ -979,19 +985,22 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="str">
+      <c r="D3" t="str">
+        <v>level_1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
         <v>zombie</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.5</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v/>
       </c>
     </row>
@@ -1005,19 +1014,22 @@
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="str">
+      <c r="D4" t="str">
+        <v>level_1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
         <v>runner</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1.2</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v/>
       </c>
     </row>
@@ -1031,19 +1043,22 @@
       <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="str">
+        <v>level_1</v>
+      </c>
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>brute</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>1.6</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v/>
       </c>
     </row>
@@ -1057,19 +1072,22 @@
       <c r="C6">
         <v>2</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="str">
+        <v>level_1</v>
+      </c>
+      <c r="E6">
         <v>2</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>zombie</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.45</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v/>
       </c>
     </row>
@@ -1083,19 +1101,22 @@
       <c r="C7">
         <v>1.8</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7" t="str">
+      <c r="D7" t="str">
+        <v>level_2</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="str">
         <v>runner</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>8</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.45</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v/>
       </c>
     </row>
@@ -1109,19 +1130,22 @@
       <c r="C8">
         <v>1.8</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="str">
+      <c r="D8" t="str">
+        <v>level_2</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="str">
         <v>zombie</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>12</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.4</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>180</v>
       </c>
     </row>
@@ -1135,19 +1159,22 @@
       <c r="C9">
         <v>1.8</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="str">
+      <c r="D9" t="str">
+        <v>level_2</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
         <v>runner</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>4</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" t="str">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="str">
         <v/>
       </c>
     </row>
@@ -1161,19 +1188,22 @@
       <c r="C10">
         <v>1.8</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="str">
+        <v>level_2</v>
+      </c>
+      <c r="E10">
         <v>2</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
         <v>brute</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>4</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1.3</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>460</v>
       </c>
     </row>
@@ -1187,19 +1217,22 @@
       <c r="C11">
         <v>1.8</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="str">
+        <v>level_2</v>
+      </c>
+      <c r="E11">
         <v>3</v>
       </c>
-      <c r="E11" t="str">
+      <c r="F11" t="str">
         <v>brute</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>3</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>1.5</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>460</v>
       </c>
     </row>
@@ -1213,19 +1246,22 @@
       <c r="C12">
         <v>1.8</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="str">
+        <v>level_2</v>
+      </c>
+      <c r="E12">
         <v>3</v>
       </c>
-      <c r="E12" t="str">
+      <c r="F12" t="str">
         <v>runner</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>8</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.4</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v/>
       </c>
     </row>
@@ -1239,25 +1275,28 @@
       <c r="C13">
         <v>1.8</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="str">
+        <v>level_2</v>
+      </c>
+      <c r="E13">
         <v>3</v>
       </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
         <v>zombie</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>10</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.4</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I13"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -500,7 +500,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="F3">
         <v>1.3</v>
@@ -865,16 +865,16 @@
         <v>dps</v>
       </c>
       <c r="B3" t="str">
-        <v>ranged</v>
+        <v>melee</v>
       </c>
       <c r="C3">
         <v>0.33</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1303,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1369,9 +1369,17 @@
         <v>150</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>roster</v>
+      </c>
+      <c r="B9" t="str">
+        <v>dps</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -577,7 +577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -803,9 +803,65 @@
         <v>0.15</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>boss_butcher</v>
+      </c>
+      <c r="B5" t="str">
+        <v>屠夫领主</v>
+      </c>
+      <c r="C5">
+        <v>40</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>1.5</v>
+      </c>
+      <c r="F5" t="str">
+        <v>150,40,40</v>
+      </c>
+      <c r="G5">
+        <v>4500</v>
+      </c>
+      <c r="H5">
+        <v>55</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.8</v>
+      </c>
+      <c r="L5">
+        <v>0.05</v>
+      </c>
+      <c r="M5">
+        <v>0.5</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0.3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -915,7 +971,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -957,7 +1013,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -986,7 +1042,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1015,7 +1071,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1044,7 +1100,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1073,7 +1129,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1096,25 +1152,25 @@
         <v>1</v>
       </c>
       <c r="B7" t="str">
-        <v>第2关 · 猛攻</v>
+        <v>第2关 · 前哨</v>
       </c>
       <c r="C7">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D7" t="str">
-        <v>level_2</v>
+        <v>c1_early</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" t="str">
-        <v>runner</v>
+        <v>zombie</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -1125,13 +1181,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="str">
-        <v>第2关 · 猛攻</v>
+        <v>第2关 · 前哨</v>
       </c>
       <c r="C8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D8" t="str">
-        <v>level_2</v>
+        <v>c1_early</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1140,13 +1196,13 @@
         <v>zombie</v>
       </c>
       <c r="G8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8">
-        <v>0.4</v>
-      </c>
-      <c r="I8">
-        <v>180</v>
+        <v>0.5</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1154,13 +1210,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="str">
-        <v>第2关 · 猛攻</v>
+        <v>第2关 · 前哨</v>
       </c>
       <c r="C9">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D9" t="str">
-        <v>level_2</v>
+        <v>c1_early</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1183,13 +1239,13 @@
         <v>1</v>
       </c>
       <c r="B10" t="str">
-        <v>第2关 · 猛攻</v>
+        <v>第2关 · 前哨</v>
       </c>
       <c r="C10">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D10" t="str">
-        <v>level_2</v>
+        <v>c1_early</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -1198,13 +1254,13 @@
         <v>brute</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>1.3</v>
-      </c>
-      <c r="I10">
-        <v>460</v>
+        <v>1.6</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1212,28 +1268,28 @@
         <v>1</v>
       </c>
       <c r="B11" t="str">
-        <v>第2关 · 猛攻</v>
+        <v>第2关 · 前哨</v>
       </c>
       <c r="C11">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D11" t="str">
-        <v>level_2</v>
+        <v>c1_early</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>brute</v>
+        <v>zombie</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H11">
-        <v>1.5</v>
-      </c>
-      <c r="I11">
-        <v>460</v>
+        <v>0.45</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1241,25 +1297,25 @@
         <v>1</v>
       </c>
       <c r="B12" t="str">
-        <v>第2关 · 猛攻</v>
+        <v>第2关 · 前哨</v>
       </c>
       <c r="C12">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D12" t="str">
-        <v>level_2</v>
+        <v>c1_early</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
         <v>runner</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -1267,36 +1323,1515 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="str">
-        <v>第2关 · 猛攻</v>
+        <v>第3关 · 溃堤</v>
       </c>
       <c r="C13">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="D13" t="str">
-        <v>level_2</v>
+        <v>c1_early</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13" t="str">
-        <v>zombie</v>
+        <v>runner</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H13">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="str">
+        <v>第3关 · 溃堤</v>
+      </c>
+      <c r="C14">
+        <v>1.9</v>
+      </c>
+      <c r="D14" t="str">
+        <v>c1_early</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G14">
+        <v>12</v>
+      </c>
+      <c r="H14">
+        <v>0.4</v>
+      </c>
+      <c r="I14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="str">
+        <v>第3关 · 溃堤</v>
+      </c>
+      <c r="C15">
+        <v>1.9</v>
+      </c>
+      <c r="D15" t="str">
+        <v>c1_early</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="str">
+        <v>第3关 · 溃堤</v>
+      </c>
+      <c r="C16">
+        <v>1.9</v>
+      </c>
+      <c r="D16" t="str">
+        <v>c1_early</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>1.5</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>第3关 · 溃堤</v>
+      </c>
+      <c r="C17">
+        <v>1.9</v>
+      </c>
+      <c r="D17" t="str">
+        <v>c1_early</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>0.4</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>第3关 · 溃堤</v>
+      </c>
+      <c r="C18">
+        <v>1.9</v>
+      </c>
+      <c r="D18" t="str">
+        <v>c1_early</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+      <c r="H18">
+        <v>0.8</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>第4关 · 铁壁</v>
+      </c>
+      <c r="C19">
+        <v>1.8</v>
+      </c>
+      <c r="D19" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19">
+        <v>0.5</v>
+      </c>
+      <c r="I19">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="str">
+        <v>第4关 · 铁壁</v>
+      </c>
+      <c r="C20">
+        <v>1.8</v>
+      </c>
+      <c r="D20" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>1.3</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21" t="str">
+        <v>第4关 · 铁壁</v>
+      </c>
+      <c r="C21">
+        <v>1.8</v>
+      </c>
+      <c r="D21" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <v>1.4</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" t="str">
+        <v>第4关 · 铁壁</v>
+      </c>
+      <c r="C22">
+        <v>1.8</v>
+      </c>
+      <c r="D22" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G22">
+        <v>6</v>
+      </c>
+      <c r="H22">
+        <v>0.8</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23" t="str">
+        <v>第4关 · 铁壁</v>
+      </c>
+      <c r="C23">
+        <v>1.8</v>
+      </c>
+      <c r="D23" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>1.2</v>
+      </c>
+      <c r="I23">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24" t="str">
+        <v>第4关 · 铁壁</v>
+      </c>
+      <c r="C24">
+        <v>1.8</v>
+      </c>
+      <c r="D24" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G24">
+        <v>8</v>
+      </c>
+      <c r="H24">
+        <v>0.4</v>
+      </c>
+      <c r="I24">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>4</v>
+      </c>
+      <c r="B25" t="str">
+        <v>第5关 · 缓坡</v>
+      </c>
+      <c r="C25">
+        <v>1.8</v>
+      </c>
+      <c r="D25" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G25">
+        <v>14</v>
+      </c>
+      <c r="H25">
+        <v>0.45</v>
+      </c>
+      <c r="I25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26" t="str">
+        <v>第5关 · 缓坡</v>
+      </c>
+      <c r="C26">
+        <v>1.8</v>
+      </c>
+      <c r="D26" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
+      </c>
+      <c r="H26">
+        <v>0.5</v>
+      </c>
+      <c r="I26">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27" t="str">
+        <v>第5关 · 缓坡</v>
+      </c>
+      <c r="C27">
+        <v>1.8</v>
+      </c>
+      <c r="D27" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27">
+        <v>1.4</v>
+      </c>
+      <c r="I27">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28" t="str">
+        <v>第5关 · 缓坡</v>
+      </c>
+      <c r="C28">
+        <v>1.8</v>
+      </c>
+      <c r="D28" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+      <c r="H28">
+        <v>0.4</v>
+      </c>
+      <c r="I28">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29" t="str">
+        <v>第5关 · 缓坡</v>
+      </c>
+      <c r="C29">
+        <v>1.8</v>
+      </c>
+      <c r="D29" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+      <c r="H29">
+        <v>1.5</v>
+      </c>
+      <c r="I29">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30" t="str">
+        <v>第5关 · 缓坡</v>
+      </c>
+      <c r="C30">
+        <v>1.8</v>
+      </c>
+      <c r="D30" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30">
+        <v>0.5</v>
+      </c>
+      <c r="I30">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>5</v>
+      </c>
+      <c r="B31" t="str">
+        <v>第6关 · 夹击</v>
+      </c>
+      <c r="C31">
+        <v>1.8</v>
+      </c>
+      <c r="D31" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G31">
+        <v>12</v>
+      </c>
+      <c r="H31">
+        <v>0.4</v>
+      </c>
+      <c r="I31">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>5</v>
+      </c>
+      <c r="B32" t="str">
+        <v>第6关 · 夹击</v>
+      </c>
+      <c r="C32">
+        <v>1.8</v>
+      </c>
+      <c r="D32" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G32">
+        <v>14</v>
+      </c>
+      <c r="H32">
+        <v>0.4</v>
+      </c>
+      <c r="I32">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>5</v>
+      </c>
+      <c r="B33" t="str">
+        <v>第6关 · 夹击</v>
+      </c>
+      <c r="C33">
+        <v>1.8</v>
+      </c>
+      <c r="D33" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+      <c r="H33">
+        <v>1.3</v>
+      </c>
+      <c r="I33">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34" t="str">
+        <v>第6关 · 夹击</v>
+      </c>
+      <c r="C34">
+        <v>1.8</v>
+      </c>
+      <c r="D34" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
+      <c r="H34">
+        <v>0.7</v>
+      </c>
+      <c r="I34">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>5</v>
+      </c>
+      <c r="B35" t="str">
+        <v>第6关 · 夹击</v>
+      </c>
+      <c r="C35">
+        <v>1.8</v>
+      </c>
+      <c r="D35" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>1.4</v>
+      </c>
+      <c r="I35">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>5</v>
+      </c>
+      <c r="B36" t="str">
+        <v>第6关 · 夹击</v>
+      </c>
+      <c r="C36">
+        <v>1.8</v>
+      </c>
+      <c r="D36" t="str">
+        <v>c1_mid</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G36">
+        <v>12</v>
+      </c>
+      <c r="H36">
+        <v>0.4</v>
+      </c>
+      <c r="I36">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>6</v>
+      </c>
+      <c r="B37" t="str">
+        <v>第7关 · 壁垒</v>
+      </c>
+      <c r="C37">
+        <v>1.6</v>
+      </c>
+      <c r="D37" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G37">
+        <v>12</v>
+      </c>
+      <c r="H37">
+        <v>0.4</v>
+      </c>
+      <c r="I37">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="B38" t="str">
+        <v>第7关 · 壁垒</v>
+      </c>
+      <c r="C38">
+        <v>1.6</v>
+      </c>
+      <c r="D38" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G38">
+        <v>4</v>
+      </c>
+      <c r="H38">
+        <v>1.2</v>
+      </c>
+      <c r="I38">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>6</v>
+      </c>
+      <c r="B39" t="str">
+        <v>第7关 · 壁垒</v>
+      </c>
+      <c r="C39">
+        <v>1.6</v>
+      </c>
+      <c r="D39" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G39">
+        <v>12</v>
+      </c>
+      <c r="H39">
+        <v>0.4</v>
+      </c>
+      <c r="I39">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>6</v>
+      </c>
+      <c r="B40" t="str">
+        <v>第7关 · 壁垒</v>
+      </c>
+      <c r="C40">
+        <v>1.6</v>
+      </c>
+      <c r="D40" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>1.2</v>
+      </c>
+      <c r="I40">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>6</v>
+      </c>
+      <c r="B41" t="str">
+        <v>第7关 · 壁垒</v>
+      </c>
+      <c r="C41">
+        <v>1.6</v>
+      </c>
+      <c r="D41" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+      <c r="H41">
+        <v>0.4</v>
+      </c>
+      <c r="I41">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>6</v>
+      </c>
+      <c r="B42" t="str">
+        <v>第7关 · 壁垒</v>
+      </c>
+      <c r="C42">
+        <v>1.6</v>
+      </c>
+      <c r="D42" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42">
+        <v>1.4</v>
+      </c>
+      <c r="I42">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>6</v>
+      </c>
+      <c r="B43" t="str">
+        <v>第7关 · 壁垒</v>
+      </c>
+      <c r="C43">
+        <v>1.6</v>
+      </c>
+      <c r="D43" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G43">
+        <v>6</v>
+      </c>
+      <c r="H43">
+        <v>0.6</v>
+      </c>
+      <c r="I43">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>7</v>
+      </c>
+      <c r="B44" t="str">
+        <v>第8关 · 风暴</v>
+      </c>
+      <c r="C44">
+        <v>1.6</v>
+      </c>
+      <c r="D44" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G44">
+        <v>14</v>
+      </c>
+      <c r="H44">
+        <v>0.35</v>
+      </c>
+      <c r="I44">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>7</v>
+      </c>
+      <c r="B45" t="str">
+        <v>第8关 · 风暴</v>
+      </c>
+      <c r="C45">
+        <v>1.6</v>
+      </c>
+      <c r="D45" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G45">
+        <v>16</v>
+      </c>
+      <c r="H45">
+        <v>0.35</v>
+      </c>
+      <c r="I45">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>7</v>
+      </c>
+      <c r="B46" t="str">
+        <v>第8关 · 风暴</v>
+      </c>
+      <c r="C46">
+        <v>1.6</v>
+      </c>
+      <c r="D46" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+      <c r="H46">
+        <v>1.2</v>
+      </c>
+      <c r="I46">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>7</v>
+      </c>
+      <c r="B47" t="str">
+        <v>第8关 · 风暴</v>
+      </c>
+      <c r="C47">
+        <v>1.6</v>
+      </c>
+      <c r="D47" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
+      </c>
+      <c r="F47" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G47">
+        <v>12</v>
+      </c>
+      <c r="H47">
+        <v>0.4</v>
+      </c>
+      <c r="I47">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>7</v>
+      </c>
+      <c r="B48" t="str">
+        <v>第8关 · 风暴</v>
+      </c>
+      <c r="C48">
+        <v>1.6</v>
+      </c>
+      <c r="D48" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
+      </c>
+      <c r="F48" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G48">
+        <v>8</v>
+      </c>
+      <c r="H48">
+        <v>0.5</v>
+      </c>
+      <c r="I48">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>7</v>
+      </c>
+      <c r="B49" t="str">
+        <v>第8关 · 风暴</v>
+      </c>
+      <c r="C49">
+        <v>1.6</v>
+      </c>
+      <c r="D49" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="F49" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G49">
+        <v>3</v>
+      </c>
+      <c r="H49">
+        <v>1.3</v>
+      </c>
+      <c r="I49">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>7</v>
+      </c>
+      <c r="B50" t="str">
+        <v>第8关 · 风暴</v>
+      </c>
+      <c r="C50">
+        <v>1.6</v>
+      </c>
+      <c r="D50" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E50">
+        <v>4</v>
+      </c>
+      <c r="F50" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G50">
+        <v>6</v>
+      </c>
+      <c r="H50">
+        <v>0.6</v>
+      </c>
+      <c r="I50">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>8</v>
+      </c>
+      <c r="B51" t="str">
+        <v>第9关 · 黑潮</v>
+      </c>
+      <c r="C51">
+        <v>1.6</v>
+      </c>
+      <c r="D51" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G51">
+        <v>14</v>
+      </c>
+      <c r="H51">
+        <v>0.35</v>
+      </c>
+      <c r="I51">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>8</v>
+      </c>
+      <c r="B52" t="str">
+        <v>第9关 · 黑潮</v>
+      </c>
+      <c r="C52">
+        <v>1.6</v>
+      </c>
+      <c r="D52" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G52">
+        <v>4</v>
+      </c>
+      <c r="H52">
+        <v>1.2</v>
+      </c>
+      <c r="I52">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>8</v>
+      </c>
+      <c r="B53" t="str">
+        <v>第9关 · 黑潮</v>
+      </c>
+      <c r="C53">
+        <v>1.6</v>
+      </c>
+      <c r="D53" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G53">
+        <v>14</v>
+      </c>
+      <c r="H53">
+        <v>0.35</v>
+      </c>
+      <c r="I53">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>8</v>
+      </c>
+      <c r="B54" t="str">
+        <v>第9关 · 黑潮</v>
+      </c>
+      <c r="C54">
+        <v>1.6</v>
+      </c>
+      <c r="D54" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G54">
+        <v>4</v>
+      </c>
+      <c r="H54">
+        <v>1.2</v>
+      </c>
+      <c r="I54">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>8</v>
+      </c>
+      <c r="B55" t="str">
+        <v>第9关 · 黑潮</v>
+      </c>
+      <c r="C55">
+        <v>1.6</v>
+      </c>
+      <c r="D55" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G55">
+        <v>10</v>
+      </c>
+      <c r="H55">
+        <v>0.4</v>
+      </c>
+      <c r="I55">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>8</v>
+      </c>
+      <c r="B56" t="str">
+        <v>第9关 · 黑潮</v>
+      </c>
+      <c r="C56">
+        <v>1.6</v>
+      </c>
+      <c r="D56" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E56">
+        <v>4</v>
+      </c>
+      <c r="F56" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56">
+        <v>1.4</v>
+      </c>
+      <c r="I56">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>8</v>
+      </c>
+      <c r="B57" t="str">
+        <v>第9关 · 黑潮</v>
+      </c>
+      <c r="C57">
+        <v>1.6</v>
+      </c>
+      <c r="D57" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="E57">
+        <v>4</v>
+      </c>
+      <c r="F57" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G57">
+        <v>8</v>
+      </c>
+      <c r="H57">
+        <v>0.5</v>
+      </c>
+      <c r="I57">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>9</v>
+      </c>
+      <c r="B58" t="str">
+        <v>第10关 · 屠夫领主</v>
+      </c>
+      <c r="C58">
+        <v>1.8</v>
+      </c>
+      <c r="D58" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G58">
+        <v>14</v>
+      </c>
+      <c r="H58">
+        <v>0.35</v>
+      </c>
+      <c r="I58">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>9</v>
+      </c>
+      <c r="B59" t="str">
+        <v>第10关 · 屠夫领主</v>
+      </c>
+      <c r="C59">
+        <v>1.8</v>
+      </c>
+      <c r="D59" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G59">
+        <v>12</v>
+      </c>
+      <c r="H59">
+        <v>0.4</v>
+      </c>
+      <c r="I59">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>9</v>
+      </c>
+      <c r="B60" t="str">
+        <v>第10关 · 屠夫领主</v>
+      </c>
+      <c r="C60">
+        <v>1.8</v>
+      </c>
+      <c r="D60" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="F60" t="str">
+        <v>brute</v>
+      </c>
+      <c r="G60">
+        <v>4</v>
+      </c>
+      <c r="H60">
+        <v>1.2</v>
+      </c>
+      <c r="I60">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>9</v>
+      </c>
+      <c r="B61" t="str">
+        <v>第10关 · 屠夫领主</v>
+      </c>
+      <c r="C61">
+        <v>1.8</v>
+      </c>
+      <c r="D61" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="E61">
+        <v>3</v>
+      </c>
+      <c r="F61" t="str">
+        <v>zombie</v>
+      </c>
+      <c r="G61">
+        <v>12</v>
+      </c>
+      <c r="H61">
+        <v>0.4</v>
+      </c>
+      <c r="I61">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>9</v>
+      </c>
+      <c r="B62" t="str">
+        <v>第10关 · 屠夫领主</v>
+      </c>
+      <c r="C62">
+        <v>1.8</v>
+      </c>
+      <c r="D62" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="E62">
+        <v>3</v>
+      </c>
+      <c r="F62" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G62">
+        <v>8</v>
+      </c>
+      <c r="H62">
+        <v>0.5</v>
+      </c>
+      <c r="I62">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>9</v>
+      </c>
+      <c r="B63" t="str">
+        <v>第10关 · 屠夫领主</v>
+      </c>
+      <c r="C63">
+        <v>1.8</v>
+      </c>
+      <c r="D63" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="E63">
+        <v>4</v>
+      </c>
+      <c r="F63" t="str">
+        <v>boss_butcher</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>9</v>
+      </c>
+      <c r="B64" t="str">
+        <v>第10关 · 屠夫领主</v>
+      </c>
+      <c r="C64">
+        <v>1.8</v>
+      </c>
+      <c r="D64" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+      <c r="F64" t="str">
+        <v>runner</v>
+      </c>
+      <c r="G64">
+        <v>6</v>
+      </c>
+      <c r="H64">
+        <v>0.8</v>
+      </c>
+      <c r="I64">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I64"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1323,58 +2858,58 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>combat.minDamageRate</v>
-      </c>
-      <c r="B3">
-        <v>0.1</v>
+        <v>roster</v>
+      </c>
+      <c r="B3" t="str">
+        <v>dps</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>layout.frontMargin</v>
+        <v>combat.minDamageRate</v>
       </c>
       <c r="B4">
-        <v>360</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>layout.spacing</v>
+        <v>layout.frontMargin</v>
       </c>
       <c r="B5">
-        <v>110</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>bullet.speed</v>
+        <v>layout.spacing</v>
       </c>
       <c r="B6">
-        <v>1100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>bullet.radius</v>
+        <v>bullet.speed</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>formation.contactGap</v>
+        <v>bullet.radius</v>
       </c>
       <c r="B8">
-        <v>150</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>roster</v>
-      </c>
-      <c r="B9" t="str">
-        <v>dps</v>
+        <v>formation.contactGap</v>
+      </c>
+      <c r="B9">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -491,10 +491,10 @@
         <v>dps</v>
       </c>
       <c r="B3">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -823,7 +823,7 @@
         <v>150,40,40</v>
       </c>
       <c r="G5">
-        <v>4500</v>
+        <v>10800</v>
       </c>
       <c r="H5">
         <v>55</v>
@@ -1521,7 +1521,7 @@
         <v>0.5</v>
       </c>
       <c r="I19">
-        <v>150</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20">
@@ -1549,8 +1549,8 @@
       <c r="H20">
         <v>1.3</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
+      <c r="I20">
+        <v>790</v>
       </c>
     </row>
     <row r="21">
@@ -1578,8 +1578,8 @@
       <c r="H21">
         <v>1.4</v>
       </c>
-      <c r="I21" t="str">
-        <v/>
+      <c r="I21">
+        <v>790</v>
       </c>
     </row>
     <row r="22">
@@ -1607,8 +1607,8 @@
       <c r="H22">
         <v>0.8</v>
       </c>
-      <c r="I22" t="str">
-        <v/>
+      <c r="I22">
+        <v>155</v>
       </c>
     </row>
     <row r="23">
@@ -1637,7 +1637,7 @@
         <v>1.2</v>
       </c>
       <c r="I23">
-        <v>460</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="24">
@@ -1666,7 +1666,7 @@
         <v>0.4</v>
       </c>
       <c r="I24">
-        <v>150</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25">
@@ -1695,7 +1695,7 @@
         <v>0.45</v>
       </c>
       <c r="I25">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -1724,7 +1724,7 @@
         <v>0.5</v>
       </c>
       <c r="I26">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
@@ -1753,7 +1753,7 @@
         <v>1.4</v>
       </c>
       <c r="I27">
-        <v>460</v>
+        <v>920</v>
       </c>
     </row>
     <row r="28">
@@ -1782,7 +1782,7 @@
         <v>0.4</v>
       </c>
       <c r="I28">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29">
@@ -1811,7 +1811,7 @@
         <v>1.5</v>
       </c>
       <c r="I29">
-        <v>460</v>
+        <v>920</v>
       </c>
     </row>
     <row r="30">
@@ -1840,7 +1840,7 @@
         <v>0.5</v>
       </c>
       <c r="I30">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
@@ -1869,7 +1869,7 @@
         <v>0.4</v>
       </c>
       <c r="I31">
-        <v>90</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
@@ -1898,7 +1898,7 @@
         <v>0.4</v>
       </c>
       <c r="I32">
-        <v>160</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33">
@@ -1927,7 +1927,7 @@
         <v>1.3</v>
       </c>
       <c r="I33">
-        <v>460</v>
+        <v>780</v>
       </c>
     </row>
     <row r="34">
@@ -1956,7 +1956,7 @@
         <v>0.7</v>
       </c>
       <c r="I34">
-        <v>90</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
@@ -1985,7 +1985,7 @@
         <v>1.4</v>
       </c>
       <c r="I35">
-        <v>460</v>
+        <v>780</v>
       </c>
     </row>
     <row r="36">
@@ -2014,7 +2014,7 @@
         <v>0.4</v>
       </c>
       <c r="I36">
-        <v>160</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37">
@@ -2043,7 +2043,7 @@
         <v>0.4</v>
       </c>
       <c r="I37">
-        <v>200</v>
+        <v>480</v>
       </c>
     </row>
     <row r="38">
@@ -2072,7 +2072,7 @@
         <v>1.2</v>
       </c>
       <c r="I38">
-        <v>560</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="39">
@@ -2101,7 +2101,7 @@
         <v>0.4</v>
       </c>
       <c r="I39">
-        <v>110</v>
+        <v>265</v>
       </c>
     </row>
     <row r="40">
@@ -2130,7 +2130,7 @@
         <v>1.2</v>
       </c>
       <c r="I40">
-        <v>560</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="41">
@@ -2159,7 +2159,7 @@
         <v>0.4</v>
       </c>
       <c r="I41">
-        <v>200</v>
+        <v>480</v>
       </c>
     </row>
     <row r="42">
@@ -2188,7 +2188,7 @@
         <v>1.4</v>
       </c>
       <c r="I42">
-        <v>560</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="43">
@@ -2217,7 +2217,7 @@
         <v>0.6</v>
       </c>
       <c r="I43">
-        <v>110</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44">
@@ -2246,7 +2246,7 @@
         <v>0.35</v>
       </c>
       <c r="I44">
-        <v>110</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45">
@@ -2275,7 +2275,7 @@
         <v>0.35</v>
       </c>
       <c r="I45">
-        <v>200</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46">
@@ -2304,7 +2304,7 @@
         <v>1.2</v>
       </c>
       <c r="I46">
-        <v>560</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="47">
@@ -2333,7 +2333,7 @@
         <v>0.4</v>
       </c>
       <c r="I47">
-        <v>200</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48">
@@ -2362,7 +2362,7 @@
         <v>0.5</v>
       </c>
       <c r="I48">
-        <v>110</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49">
@@ -2391,7 +2391,7 @@
         <v>1.3</v>
       </c>
       <c r="I49">
-        <v>560</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="50">
@@ -2420,7 +2420,7 @@
         <v>0.6</v>
       </c>
       <c r="I50">
-        <v>110</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51">
@@ -2449,7 +2449,7 @@
         <v>0.35</v>
       </c>
       <c r="I51">
-        <v>220</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52">
@@ -2478,7 +2478,7 @@
         <v>1.2</v>
       </c>
       <c r="I52">
-        <v>600</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="53">
@@ -2507,7 +2507,7 @@
         <v>0.35</v>
       </c>
       <c r="I53">
-        <v>120</v>
+        <v>230</v>
       </c>
     </row>
     <row r="54">
@@ -2536,7 +2536,7 @@
         <v>1.2</v>
       </c>
       <c r="I54">
-        <v>600</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="55">
@@ -2565,7 +2565,7 @@
         <v>0.4</v>
       </c>
       <c r="I55">
-        <v>220</v>
+        <v>420</v>
       </c>
     </row>
     <row r="56">
@@ -2594,7 +2594,7 @@
         <v>1.4</v>
       </c>
       <c r="I56">
-        <v>600</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="57">
@@ -2623,7 +2623,7 @@
         <v>0.5</v>
       </c>
       <c r="I57">
-        <v>120</v>
+        <v>230</v>
       </c>
     </row>
     <row r="58">
@@ -2652,7 +2652,7 @@
         <v>0.35</v>
       </c>
       <c r="I58">
-        <v>240</v>
+        <v>575</v>
       </c>
     </row>
     <row r="59">
@@ -2681,7 +2681,7 @@
         <v>0.4</v>
       </c>
       <c r="I59">
-        <v>120</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60">
@@ -2710,7 +2710,7 @@
         <v>1.2</v>
       </c>
       <c r="I60">
-        <v>600</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="61">
@@ -2739,7 +2739,7 @@
         <v>0.4</v>
       </c>
       <c r="I61">
-        <v>240</v>
+        <v>575</v>
       </c>
     </row>
     <row r="62">
@@ -2768,7 +2768,7 @@
         <v>0.5</v>
       </c>
       <c r="I62">
-        <v>120</v>
+        <v>290</v>
       </c>
     </row>
     <row r="63">
@@ -2826,7 +2826,7 @@
         <v>0.8</v>
       </c>
       <c r="I64">
-        <v>120</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -823,7 +823,7 @@
         <v>150,40,40</v>
       </c>
       <c r="G5">
-        <v>10800</v>
+        <v>15100</v>
       </c>
       <c r="H5">
         <v>55</v>
@@ -2043,7 +2043,7 @@
         <v>0.4</v>
       </c>
       <c r="I37">
-        <v>480</v>
+        <v>670</v>
       </c>
     </row>
     <row r="38">
@@ -2072,7 +2072,7 @@
         <v>1.2</v>
       </c>
       <c r="I38">
-        <v>1345</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="39">
@@ -2101,7 +2101,7 @@
         <v>0.4</v>
       </c>
       <c r="I39">
-        <v>265</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40">
@@ -2130,7 +2130,7 @@
         <v>1.2</v>
       </c>
       <c r="I40">
-        <v>1345</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="41">
@@ -2159,7 +2159,7 @@
         <v>0.4</v>
       </c>
       <c r="I41">
-        <v>480</v>
+        <v>670</v>
       </c>
     </row>
     <row r="42">
@@ -2188,7 +2188,7 @@
         <v>1.4</v>
       </c>
       <c r="I42">
-        <v>1345</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="43">
@@ -2217,7 +2217,7 @@
         <v>0.6</v>
       </c>
       <c r="I43">
-        <v>265</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44">
@@ -2652,7 +2652,7 @@
         <v>0.35</v>
       </c>
       <c r="I58">
-        <v>575</v>
+        <v>805</v>
       </c>
     </row>
     <row r="59">
@@ -2681,7 +2681,7 @@
         <v>0.4</v>
       </c>
       <c r="I59">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="60">
@@ -2710,7 +2710,7 @@
         <v>1.2</v>
       </c>
       <c r="I60">
-        <v>1440</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="61">
@@ -2739,7 +2739,7 @@
         <v>0.4</v>
       </c>
       <c r="I61">
-        <v>575</v>
+        <v>805</v>
       </c>
     </row>
     <row r="62">
@@ -2768,7 +2768,7 @@
         <v>0.5</v>
       </c>
       <c r="I62">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
     <row r="63">
@@ -2826,7 +2826,7 @@
         <v>0.8</v>
       </c>
       <c r="I64">
-        <v>290</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -2838,7 +2838,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2858,63 +2858,71 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>roster</v>
-      </c>
-      <c r="B3" t="str">
-        <v>dps</v>
+        <v>squadCap</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>combat.minDamageRate</v>
-      </c>
-      <c r="B4">
-        <v>0.1</v>
+        <v>roster</v>
+      </c>
+      <c r="B4" t="str">
+        <v>dps</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>layout.frontMargin</v>
+        <v>combat.minDamageRate</v>
       </c>
       <c r="B5">
-        <v>360</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>layout.spacing</v>
+        <v>layout.frontMargin</v>
       </c>
       <c r="B6">
-        <v>110</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>bullet.speed</v>
+        <v>layout.spacing</v>
       </c>
       <c r="B7">
-        <v>1100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>bullet.radius</v>
+        <v>bullet.speed</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>bullet.radius</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v>formation.contactGap</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -2043,7 +2043,7 @@
         <v>0.4</v>
       </c>
       <c r="I37">
-        <v>670</v>
+        <v>770</v>
       </c>
     </row>
     <row r="38">
@@ -2072,7 +2072,7 @@
         <v>1.2</v>
       </c>
       <c r="I38">
-        <v>1885</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="39">
@@ -2101,7 +2101,7 @@
         <v>0.4</v>
       </c>
       <c r="I39">
-        <v>370</v>
+        <v>426</v>
       </c>
     </row>
     <row r="40">
@@ -2130,7 +2130,7 @@
         <v>1.2</v>
       </c>
       <c r="I40">
-        <v>1885</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="41">
@@ -2159,7 +2159,7 @@
         <v>0.4</v>
       </c>
       <c r="I41">
-        <v>670</v>
+        <v>770</v>
       </c>
     </row>
     <row r="42">
@@ -2188,7 +2188,7 @@
         <v>1.4</v>
       </c>
       <c r="I42">
-        <v>1885</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="43">
@@ -2217,7 +2217,7 @@
         <v>0.6</v>
       </c>
       <c r="I43">
-        <v>370</v>
+        <v>426</v>
       </c>
     </row>
     <row r="44">
@@ -2796,8 +2796,8 @@
       <c r="H63">
         <v>1</v>
       </c>
-      <c r="I63" t="str">
-        <v/>
+      <c r="I63">
+        <v>36000</v>
       </c>
     </row>
     <row r="64">
@@ -2869,7 +2869,7 @@
         <v>roster</v>
       </c>
       <c r="B4" t="str">
-        <v>dps</v>
+        <v>tank,dps</v>
       </c>
     </row>
     <row r="5">

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -577,7 +577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:S5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -634,6 +634,9 @@
       <c r="R1" t="str">
         <v>dmgReduce</v>
       </c>
+      <c r="S1" t="str">
+        <v>exp</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -690,6 +693,9 @@
       <c r="R2">
         <v>0</v>
       </c>
+      <c r="S2">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -746,6 +752,9 @@
       <c r="R3">
         <v>0</v>
       </c>
+      <c r="S3">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -802,6 +811,9 @@
       <c r="R4">
         <v>0.15</v>
       </c>
+      <c r="S4">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -858,10 +870,13 @@
       <c r="R5">
         <v>0.3</v>
       </c>
+      <c r="S5">
+        <v>200</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2838,7 +2853,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2874,55 +2889,87 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>combat.minDamageRate</v>
+        <v>charGrowth.expBase</v>
       </c>
       <c r="B5">
-        <v>0.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>layout.frontMargin</v>
+        <v>charGrowth.expGrowthPerLevel</v>
       </c>
       <c r="B6">
-        <v>360</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>layout.spacing</v>
+        <v>charGrowth.statGrowthPerLevel</v>
       </c>
       <c r="B7">
-        <v>110</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>bullet.speed</v>
+        <v>charGrowth.maxLevel</v>
       </c>
       <c r="B8">
-        <v>1100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>bullet.radius</v>
+        <v>combat.minDamageRate</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>layout.frontMargin</v>
+      </c>
+      <c r="B10">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>layout.spacing</v>
+      </c>
+      <c r="B11">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>bullet.speed</v>
+      </c>
+      <c r="B12">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>bullet.radius</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
         <v>formation.contactGap</v>
       </c>
-      <c r="B10">
+      <c r="B14">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B14"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,6 +444,9 @@
       <c r="M1" t="str">
         <v>dmgReduce</v>
       </c>
+      <c r="N1" t="str">
+        <v>moveSpeed</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -485,6 +488,9 @@
       <c r="M2">
         <v>0.1</v>
       </c>
+      <c r="N2">
+        <v>300</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -526,6 +532,9 @@
       <c r="M3">
         <v>0</v>
       </c>
+      <c r="N3">
+        <v>300</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -567,10 +576,13 @@
       <c r="M4">
         <v>0</v>
       </c>
+      <c r="N4">
+        <v>220</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,52 +599,52 @@
         <v>name</v>
       </c>
       <c r="C1" t="str">
-        <v>speed</v>
+        <v>radius</v>
       </c>
       <c r="D1" t="str">
-        <v>radius</v>
+        <v>attackInterval</v>
       </c>
       <c r="E1" t="str">
-        <v>attackInterval</v>
+        <v>color</v>
       </c>
       <c r="F1" t="str">
-        <v>color</v>
+        <v>hp</v>
       </c>
       <c r="G1" t="str">
-        <v>hp</v>
+        <v>atk</v>
       </c>
       <c r="H1" t="str">
-        <v>atk</v>
+        <v>def</v>
       </c>
       <c r="I1" t="str">
-        <v>def</v>
+        <v>range</v>
       </c>
       <c r="J1" t="str">
-        <v>range</v>
+        <v>attackSpeed</v>
       </c>
       <c r="K1" t="str">
-        <v>attackSpeed</v>
+        <v>critRate</v>
       </c>
       <c r="L1" t="str">
-        <v>critRate</v>
+        <v>critDmg</v>
       </c>
       <c r="M1" t="str">
-        <v>critDmg</v>
+        <v>dodgeRate</v>
       </c>
       <c r="N1" t="str">
-        <v>dodgeRate</v>
+        <v>blockRate</v>
       </c>
       <c r="O1" t="str">
-        <v>blockRate</v>
+        <v>blockRatio</v>
       </c>
       <c r="P1" t="str">
-        <v>blockRatio</v>
+        <v>dmgBonus</v>
       </c>
       <c r="Q1" t="str">
-        <v>dmgBonus</v>
+        <v>dmgReduce</v>
       </c>
       <c r="R1" t="str">
-        <v>dmgReduce</v>
+        <v>moveSpeed</v>
       </c>
       <c r="S1" t="str">
         <v>exp</v>
@@ -646,52 +658,52 @@
         <v>丧尸</v>
       </c>
       <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>0.8</v>
+      </c>
+      <c r="E2" t="str">
+        <v>230,70,70</v>
+      </c>
+      <c r="F2">
+        <v>120</v>
+      </c>
+      <c r="G2">
+        <v>18</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0.05</v>
+      </c>
+      <c r="L2">
+        <v>0.5</v>
+      </c>
+      <c r="M2">
+        <v>0.05</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
         <v>90</v>
-      </c>
-      <c r="D2">
-        <v>28</v>
-      </c>
-      <c r="E2">
-        <v>0.8</v>
-      </c>
-      <c r="F2" t="str">
-        <v>230,70,70</v>
-      </c>
-      <c r="G2">
-        <v>120</v>
-      </c>
-      <c r="H2">
-        <v>18</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>0.05</v>
-      </c>
-      <c r="M2">
-        <v>0.5</v>
-      </c>
-      <c r="N2">
-        <v>0.05</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
       </c>
       <c r="S2">
         <v>5</v>
@@ -705,52 +717,52 @@
         <v>疾行者</v>
       </c>
       <c r="C3">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>0.6</v>
+      </c>
+      <c r="E3" t="str">
+        <v>240,150,60</v>
+      </c>
+      <c r="F3">
+        <v>70</v>
+      </c>
+      <c r="G3">
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.4</v>
+      </c>
+      <c r="K3">
+        <v>0.05</v>
+      </c>
+      <c r="L3">
+        <v>0.5</v>
+      </c>
+      <c r="M3">
+        <v>0.15</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
         <v>175</v>
-      </c>
-      <c r="D3">
-        <v>22</v>
-      </c>
-      <c r="E3">
-        <v>0.6</v>
-      </c>
-      <c r="F3" t="str">
-        <v>240,150,60</v>
-      </c>
-      <c r="G3">
-        <v>70</v>
-      </c>
-      <c r="H3">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>1.4</v>
-      </c>
-      <c r="L3">
-        <v>0.05</v>
-      </c>
-      <c r="M3">
-        <v>0.5</v>
-      </c>
-      <c r="N3">
-        <v>0.15</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
       </c>
       <c r="S3">
         <v>4</v>
@@ -764,52 +776,52 @@
         <v>重装</v>
       </c>
       <c r="C4">
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>1.2</v>
+      </c>
+      <c r="E4" t="str">
+        <v>170,80,200</v>
+      </c>
+      <c r="F4">
+        <v>360</v>
+      </c>
+      <c r="G4">
+        <v>30</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.8</v>
+      </c>
+      <c r="K4">
+        <v>0.05</v>
+      </c>
+      <c r="L4">
+        <v>0.5</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0.15</v>
+      </c>
+      <c r="R4">
         <v>55</v>
-      </c>
-      <c r="D4">
-        <v>40</v>
-      </c>
-      <c r="E4">
-        <v>1.2</v>
-      </c>
-      <c r="F4" t="str">
-        <v>170,80,200</v>
-      </c>
-      <c r="G4">
-        <v>360</v>
-      </c>
-      <c r="H4">
-        <v>30</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0.8</v>
-      </c>
-      <c r="L4">
-        <v>0.05</v>
-      </c>
-      <c r="M4">
-        <v>0.5</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0.15</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -823,52 +835,52 @@
         <v>屠夫领主</v>
       </c>
       <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>1.5</v>
+      </c>
+      <c r="E5" t="str">
+        <v>150,40,40</v>
+      </c>
+      <c r="F5">
+        <v>15100</v>
+      </c>
+      <c r="G5">
+        <v>55</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.8</v>
+      </c>
+      <c r="K5">
+        <v>0.05</v>
+      </c>
+      <c r="L5">
+        <v>0.5</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0.3</v>
+      </c>
+      <c r="R5">
         <v>40</v>
-      </c>
-      <c r="D5">
-        <v>60</v>
-      </c>
-      <c r="E5">
-        <v>1.5</v>
-      </c>
-      <c r="F5" t="str">
-        <v>150,40,40</v>
-      </c>
-      <c r="G5">
-        <v>15100</v>
-      </c>
-      <c r="H5">
-        <v>55</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0.8</v>
-      </c>
-      <c r="L5">
-        <v>0.05</v>
-      </c>
-      <c r="M5">
-        <v>0.5</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0.3</v>
       </c>
       <c r="S5">
         <v>200</v>
@@ -883,7 +895,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -896,15 +908,12 @@
         <v>fireInterval</v>
       </c>
       <c r="D1" t="str">
-        <v>moveSpeed</v>
+        <v>advanceLimit</v>
       </c>
       <c r="E1" t="str">
-        <v>advanceLimit</v>
+        <v>healPerSec</v>
       </c>
       <c r="F1" t="str">
-        <v>healPerSec</v>
-      </c>
-      <c r="G1" t="str">
         <v>size</v>
       </c>
     </row>
@@ -919,15 +928,12 @@
         <v>0.5</v>
       </c>
       <c r="D2">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="E2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
         <v>74</v>
       </c>
     </row>
@@ -942,15 +948,12 @@
         <v>0.33</v>
       </c>
       <c r="D3">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="E3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
         <v>52</v>
       </c>
     </row>
@@ -968,18 +971,15 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>16</v>
-      </c>
-      <c r="G4">
         <v>52</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -996,7 +996,7 @@
         <v>levelName</v>
       </c>
       <c r="C1" t="str">
-        <v>waveGap</v>
+        <v>distance</v>
       </c>
       <c r="D1" t="str">
         <v>dropGroup</v>
@@ -1025,7 +1025,7 @@
         <v>第1关 · 试炼</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D2" t="str">
         <v>c1_early</v>
@@ -1054,7 +1054,7 @@
         <v>第1关 · 试炼</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D3" t="str">
         <v>c1_early</v>
@@ -1083,7 +1083,7 @@
         <v>第1关 · 试炼</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D4" t="str">
         <v>c1_early</v>
@@ -1112,7 +1112,7 @@
         <v>第1关 · 试炼</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D5" t="str">
         <v>c1_early</v>
@@ -1141,7 +1141,7 @@
         <v>第1关 · 试炼</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D6" t="str">
         <v>c1_early</v>
@@ -1170,7 +1170,7 @@
         <v>第2关 · 前哨</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D7" t="str">
         <v>c1_early</v>
@@ -1199,7 +1199,7 @@
         <v>第2关 · 前哨</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D8" t="str">
         <v>c1_early</v>
@@ -1228,7 +1228,7 @@
         <v>第2关 · 前哨</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D9" t="str">
         <v>c1_early</v>
@@ -1257,7 +1257,7 @@
         <v>第2关 · 前哨</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D10" t="str">
         <v>c1_early</v>
@@ -1286,7 +1286,7 @@
         <v>第2关 · 前哨</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D11" t="str">
         <v>c1_early</v>
@@ -1315,7 +1315,7 @@
         <v>第2关 · 前哨</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D12" t="str">
         <v>c1_early</v>
@@ -1344,7 +1344,7 @@
         <v>第3关 · 溃堤</v>
       </c>
       <c r="C13">
-        <v>1.9</v>
+        <v>600</v>
       </c>
       <c r="D13" t="str">
         <v>c1_early</v>
@@ -1373,7 +1373,7 @@
         <v>第3关 · 溃堤</v>
       </c>
       <c r="C14">
-        <v>1.9</v>
+        <v>600</v>
       </c>
       <c r="D14" t="str">
         <v>c1_early</v>
@@ -1402,7 +1402,7 @@
         <v>第3关 · 溃堤</v>
       </c>
       <c r="C15">
-        <v>1.9</v>
+        <v>600</v>
       </c>
       <c r="D15" t="str">
         <v>c1_early</v>
@@ -1431,7 +1431,7 @@
         <v>第3关 · 溃堤</v>
       </c>
       <c r="C16">
-        <v>1.9</v>
+        <v>600</v>
       </c>
       <c r="D16" t="str">
         <v>c1_early</v>
@@ -1460,7 +1460,7 @@
         <v>第3关 · 溃堤</v>
       </c>
       <c r="C17">
-        <v>1.9</v>
+        <v>600</v>
       </c>
       <c r="D17" t="str">
         <v>c1_early</v>
@@ -1489,7 +1489,7 @@
         <v>第3关 · 溃堤</v>
       </c>
       <c r="C18">
-        <v>1.9</v>
+        <v>600</v>
       </c>
       <c r="D18" t="str">
         <v>c1_early</v>
@@ -1518,7 +1518,7 @@
         <v>第4关 · 铁壁</v>
       </c>
       <c r="C19">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D19" t="str">
         <v>c1_mid</v>
@@ -1547,7 +1547,7 @@
         <v>第4关 · 铁壁</v>
       </c>
       <c r="C20">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D20" t="str">
         <v>c1_mid</v>
@@ -1576,7 +1576,7 @@
         <v>第4关 · 铁壁</v>
       </c>
       <c r="C21">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D21" t="str">
         <v>c1_mid</v>
@@ -1605,7 +1605,7 @@
         <v>第4关 · 铁壁</v>
       </c>
       <c r="C22">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D22" t="str">
         <v>c1_mid</v>
@@ -1634,7 +1634,7 @@
         <v>第4关 · 铁壁</v>
       </c>
       <c r="C23">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D23" t="str">
         <v>c1_mid</v>
@@ -1663,7 +1663,7 @@
         <v>第4关 · 铁壁</v>
       </c>
       <c r="C24">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D24" t="str">
         <v>c1_mid</v>
@@ -1692,7 +1692,7 @@
         <v>第5关 · 缓坡</v>
       </c>
       <c r="C25">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D25" t="str">
         <v>c1_mid</v>
@@ -1721,7 +1721,7 @@
         <v>第5关 · 缓坡</v>
       </c>
       <c r="C26">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D26" t="str">
         <v>c1_mid</v>
@@ -1750,7 +1750,7 @@
         <v>第5关 · 缓坡</v>
       </c>
       <c r="C27">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D27" t="str">
         <v>c1_mid</v>
@@ -1779,7 +1779,7 @@
         <v>第5关 · 缓坡</v>
       </c>
       <c r="C28">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D28" t="str">
         <v>c1_mid</v>
@@ -1808,7 +1808,7 @@
         <v>第5关 · 缓坡</v>
       </c>
       <c r="C29">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D29" t="str">
         <v>c1_mid</v>
@@ -1837,7 +1837,7 @@
         <v>第5关 · 缓坡</v>
       </c>
       <c r="C30">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D30" t="str">
         <v>c1_mid</v>
@@ -1866,7 +1866,7 @@
         <v>第6关 · 夹击</v>
       </c>
       <c r="C31">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D31" t="str">
         <v>c1_mid</v>
@@ -1895,7 +1895,7 @@
         <v>第6关 · 夹击</v>
       </c>
       <c r="C32">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D32" t="str">
         <v>c1_mid</v>
@@ -1924,7 +1924,7 @@
         <v>第6关 · 夹击</v>
       </c>
       <c r="C33">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D33" t="str">
         <v>c1_mid</v>
@@ -1953,7 +1953,7 @@
         <v>第6关 · 夹击</v>
       </c>
       <c r="C34">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D34" t="str">
         <v>c1_mid</v>
@@ -1982,7 +1982,7 @@
         <v>第6关 · 夹击</v>
       </c>
       <c r="C35">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D35" t="str">
         <v>c1_mid</v>
@@ -2011,7 +2011,7 @@
         <v>第6关 · 夹击</v>
       </c>
       <c r="C36">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D36" t="str">
         <v>c1_mid</v>
@@ -2040,7 +2040,7 @@
         <v>第7关 · 壁垒</v>
       </c>
       <c r="C37">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D37" t="str">
         <v>c1_late</v>
@@ -2069,7 +2069,7 @@
         <v>第7关 · 壁垒</v>
       </c>
       <c r="C38">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D38" t="str">
         <v>c1_late</v>
@@ -2098,7 +2098,7 @@
         <v>第7关 · 壁垒</v>
       </c>
       <c r="C39">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D39" t="str">
         <v>c1_late</v>
@@ -2127,7 +2127,7 @@
         <v>第7关 · 壁垒</v>
       </c>
       <c r="C40">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D40" t="str">
         <v>c1_late</v>
@@ -2156,7 +2156,7 @@
         <v>第7关 · 壁垒</v>
       </c>
       <c r="C41">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D41" t="str">
         <v>c1_late</v>
@@ -2185,7 +2185,7 @@
         <v>第7关 · 壁垒</v>
       </c>
       <c r="C42">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D42" t="str">
         <v>c1_late</v>
@@ -2214,7 +2214,7 @@
         <v>第7关 · 壁垒</v>
       </c>
       <c r="C43">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D43" t="str">
         <v>c1_late</v>
@@ -2243,7 +2243,7 @@
         <v>第8关 · 风暴</v>
       </c>
       <c r="C44">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D44" t="str">
         <v>c1_late</v>
@@ -2272,7 +2272,7 @@
         <v>第8关 · 风暴</v>
       </c>
       <c r="C45">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D45" t="str">
         <v>c1_late</v>
@@ -2301,7 +2301,7 @@
         <v>第8关 · 风暴</v>
       </c>
       <c r="C46">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D46" t="str">
         <v>c1_late</v>
@@ -2330,7 +2330,7 @@
         <v>第8关 · 风暴</v>
       </c>
       <c r="C47">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D47" t="str">
         <v>c1_late</v>
@@ -2359,7 +2359,7 @@
         <v>第8关 · 风暴</v>
       </c>
       <c r="C48">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D48" t="str">
         <v>c1_late</v>
@@ -2388,7 +2388,7 @@
         <v>第8关 · 风暴</v>
       </c>
       <c r="C49">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D49" t="str">
         <v>c1_late</v>
@@ -2417,7 +2417,7 @@
         <v>第8关 · 风暴</v>
       </c>
       <c r="C50">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D50" t="str">
         <v>c1_late</v>
@@ -2446,7 +2446,7 @@
         <v>第9关 · 黑潮</v>
       </c>
       <c r="C51">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D51" t="str">
         <v>c1_late</v>
@@ -2475,7 +2475,7 @@
         <v>第9关 · 黑潮</v>
       </c>
       <c r="C52">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D52" t="str">
         <v>c1_late</v>
@@ -2504,7 +2504,7 @@
         <v>第9关 · 黑潮</v>
       </c>
       <c r="C53">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D53" t="str">
         <v>c1_late</v>
@@ -2533,7 +2533,7 @@
         <v>第9关 · 黑潮</v>
       </c>
       <c r="C54">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D54" t="str">
         <v>c1_late</v>
@@ -2562,7 +2562,7 @@
         <v>第9关 · 黑潮</v>
       </c>
       <c r="C55">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D55" t="str">
         <v>c1_late</v>
@@ -2591,7 +2591,7 @@
         <v>第9关 · 黑潮</v>
       </c>
       <c r="C56">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D56" t="str">
         <v>c1_late</v>
@@ -2620,7 +2620,7 @@
         <v>第9关 · 黑潮</v>
       </c>
       <c r="C57">
-        <v>1.6</v>
+        <v>600</v>
       </c>
       <c r="D57" t="str">
         <v>c1_late</v>
@@ -2649,7 +2649,7 @@
         <v>第10关 · 屠夫领主</v>
       </c>
       <c r="C58">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D58" t="str">
         <v>c1_boss</v>
@@ -2678,7 +2678,7 @@
         <v>第10关 · 屠夫领主</v>
       </c>
       <c r="C59">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D59" t="str">
         <v>c1_boss</v>
@@ -2707,7 +2707,7 @@
         <v>第10关 · 屠夫领主</v>
       </c>
       <c r="C60">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D60" t="str">
         <v>c1_boss</v>
@@ -2736,7 +2736,7 @@
         <v>第10关 · 屠夫领主</v>
       </c>
       <c r="C61">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D61" t="str">
         <v>c1_boss</v>
@@ -2765,7 +2765,7 @@
         <v>第10关 · 屠夫领主</v>
       </c>
       <c r="C62">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D62" t="str">
         <v>c1_boss</v>
@@ -2794,7 +2794,7 @@
         <v>第10关 · 屠夫领主</v>
       </c>
       <c r="C63">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D63" t="str">
         <v>c1_boss</v>
@@ -2823,7 +2823,7 @@
         <v>第10关 · 屠夫领主</v>
       </c>
       <c r="C64">
-        <v>1.8</v>
+        <v>600</v>
       </c>
       <c r="D64" t="str">
         <v>c1_boss</v>

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -1385,13 +1385,13 @@
         <v>zombie</v>
       </c>
       <c r="G14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H14">
         <v>0.4</v>
       </c>
       <c r="I14">
-        <v>150</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -1414,7 +1414,7 @@
         <v>runner</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1443,7 +1443,7 @@
         <v>brute</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>1.5</v>
@@ -1472,7 +1472,7 @@
         <v>zombie</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H17">
         <v>0.4</v>
@@ -2058,7 +2058,7 @@
         <v>0.4</v>
       </c>
       <c r="I37">
-        <v>770</v>
+        <v>730</v>
       </c>
     </row>
     <row r="38">
@@ -2087,7 +2087,7 @@
         <v>1.2</v>
       </c>
       <c r="I38">
-        <v>2168</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="39">
@@ -2116,7 +2116,7 @@
         <v>0.4</v>
       </c>
       <c r="I39">
-        <v>426</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40">
@@ -2145,7 +2145,7 @@
         <v>1.2</v>
       </c>
       <c r="I40">
-        <v>2168</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="41">
@@ -2174,7 +2174,7 @@
         <v>0.4</v>
       </c>
       <c r="I41">
-        <v>770</v>
+        <v>730</v>
       </c>
     </row>
     <row r="42">
@@ -2203,7 +2203,7 @@
         <v>1.4</v>
       </c>
       <c r="I42">
-        <v>2168</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="43">
@@ -2232,7 +2232,7 @@
         <v>0.6</v>
       </c>
       <c r="I43">
-        <v>426</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44">
@@ -2812,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>36000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="64">

--- a/tools/config-xlsx/battle.xlsx
+++ b/tools/config-xlsx/battle.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:S4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,6 +447,21 @@
       <c r="N1" t="str">
         <v>moveSpeed</v>
       </c>
+      <c r="O1" t="str">
+        <v>skillHaste</v>
+      </c>
+      <c r="P1" t="str">
+        <v>basicDmgBonus</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>skillDmgBonus</v>
+      </c>
+      <c r="R1" t="str">
+        <v>singleDmgBonus</v>
+      </c>
+      <c r="S1" t="str">
+        <v>aoeDmgBonus</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -491,6 +506,21 @@
       <c r="N2">
         <v>300</v>
       </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -535,6 +565,21 @@
       <c r="N3">
         <v>300</v>
       </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -579,17 +624,32 @@
       <c r="N4">
         <v>220</v>
       </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:X5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -647,6 +707,21 @@
         <v>moveSpeed</v>
       </c>
       <c r="S1" t="str">
+        <v>skillHaste</v>
+      </c>
+      <c r="T1" t="str">
+        <v>basicDmgBonus</v>
+      </c>
+      <c r="U1" t="str">
+        <v>skillDmgBonus</v>
+      </c>
+      <c r="V1" t="str">
+        <v>singleDmgBonus</v>
+      </c>
+      <c r="W1" t="str">
+        <v>aoeDmgBonus</v>
+      </c>
+      <c r="X1" t="str">
         <v>exp</v>
       </c>
     </row>
@@ -706,6 +781,21 @@
         <v>90</v>
       </c>
       <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
         <v>5</v>
       </c>
     </row>
@@ -765,6 +855,21 @@
         <v>175</v>
       </c>
       <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
         <v>4</v>
       </c>
     </row>
@@ -824,6 +929,21 @@
         <v>55</v>
       </c>
       <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
         <v>10</v>
       </c>
     </row>
@@ -883,12 +1003,27 @@
         <v>40</v>
       </c>
       <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
         <v>200</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -986,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:J64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1016,6 +1151,9 @@
       <c r="I1" t="str">
         <v>hp</v>
       </c>
+      <c r="J1" t="str">
+        <v>enemyScale</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1045,6 +1183,9 @@
       <c r="I2" t="str">
         <v/>
       </c>
+      <c r="J2">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -1074,6 +1215,9 @@
       <c r="I3" t="str">
         <v/>
       </c>
+      <c r="J3">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -1103,6 +1247,9 @@
       <c r="I4" t="str">
         <v/>
       </c>
+      <c r="J4">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -1132,6 +1279,9 @@
       <c r="I5" t="str">
         <v/>
       </c>
+      <c r="J5">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -1160,6 +1310,9 @@
       </c>
       <c r="I6" t="str">
         <v/>
+      </c>
+      <c r="J6">
+        <v>0.88</v>
       </c>
     </row>
     <row r="7">
@@ -1190,6 +1343,9 @@
       <c r="I7" t="str">
         <v/>
       </c>
+      <c r="J7">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -1219,6 +1375,9 @@
       <c r="I8" t="str">
         <v/>
       </c>
+      <c r="J8">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -1248,6 +1407,9 @@
       <c r="I9" t="str">
         <v/>
       </c>
+      <c r="J9">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -1277,6 +1439,9 @@
       <c r="I10" t="str">
         <v/>
       </c>
+      <c r="J10">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -1306,6 +1471,9 @@
       <c r="I11" t="str">
         <v/>
       </c>
+      <c r="J11">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -1335,6 +1503,9 @@
       <c r="I12" t="str">
         <v/>
       </c>
+      <c r="J12">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -1364,6 +1535,9 @@
       <c r="I13" t="str">
         <v/>
       </c>
+      <c r="J13">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -1393,6 +1567,9 @@
       <c r="I14">
         <v>110</v>
       </c>
+      <c r="J14">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1422,6 +1599,9 @@
       <c r="I15" t="str">
         <v/>
       </c>
+      <c r="J15">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1451,6 +1631,9 @@
       <c r="I16" t="str">
         <v/>
       </c>
+      <c r="J16">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1480,6 +1663,9 @@
       <c r="I17" t="str">
         <v/>
       </c>
+      <c r="J17">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1509,6 +1695,9 @@
       <c r="I18" t="str">
         <v/>
       </c>
+      <c r="J18">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1538,6 +1727,9 @@
       <c r="I19">
         <v>330</v>
       </c>
+      <c r="J19">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1567,6 +1759,9 @@
       <c r="I20">
         <v>790</v>
       </c>
+      <c r="J20">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -1596,6 +1791,9 @@
       <c r="I21">
         <v>790</v>
       </c>
+      <c r="J21">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1625,6 +1823,9 @@
       <c r="I22">
         <v>155</v>
       </c>
+      <c r="J22">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1654,6 +1855,9 @@
       <c r="I23">
         <v>1010</v>
       </c>
+      <c r="J23">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1683,6 +1887,9 @@
       <c r="I24">
         <v>330</v>
       </c>
+      <c r="J24">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1712,6 +1919,9 @@
       <c r="I25">
         <v>300</v>
       </c>
+      <c r="J25">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1741,6 +1951,9 @@
       <c r="I26">
         <v>180</v>
       </c>
+      <c r="J26">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1770,6 +1983,9 @@
       <c r="I27">
         <v>920</v>
       </c>
+      <c r="J27">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1799,6 +2015,9 @@
       <c r="I28">
         <v>300</v>
       </c>
+      <c r="J28">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1828,6 +2047,9 @@
       <c r="I29">
         <v>920</v>
       </c>
+      <c r="J29">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1857,6 +2079,9 @@
       <c r="I30">
         <v>180</v>
       </c>
+      <c r="J30">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1886,6 +2111,9 @@
       <c r="I31">
         <v>155</v>
       </c>
+      <c r="J31">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1915,6 +2143,9 @@
       <c r="I32">
         <v>275</v>
       </c>
+      <c r="J32">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1944,6 +2175,9 @@
       <c r="I33">
         <v>780</v>
       </c>
+      <c r="J33">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1973,6 +2207,9 @@
       <c r="I34">
         <v>155</v>
       </c>
+      <c r="J34">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -2002,6 +2239,9 @@
       <c r="I35">
         <v>780</v>
       </c>
+      <c r="J35">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -2031,6 +2271,9 @@
       <c r="I36">
         <v>275</v>
       </c>
+      <c r="J36">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -2060,6 +2303,9 @@
       <c r="I37">
         <v>730</v>
       </c>
+      <c r="J37">
+        <v>2.56</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -2089,6 +2335,9 @@
       <c r="I38">
         <v>2060</v>
       </c>
+      <c r="J38">
+        <v>2.56</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -2118,6 +2367,9 @@
       <c r="I39">
         <v>405</v>
       </c>
+      <c r="J39">
+        <v>2.56</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -2147,6 +2399,9 @@
       <c r="I40">
         <v>2060</v>
       </c>
+      <c r="J40">
+        <v>2.56</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -2176,6 +2431,9 @@
       <c r="I41">
         <v>730</v>
       </c>
+      <c r="J41">
+        <v>2.56</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -2205,6 +2463,9 @@
       <c r="I42">
         <v>2060</v>
       </c>
+      <c r="J42">
+        <v>2.56</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -2234,6 +2495,9 @@
       <c r="I43">
         <v>405</v>
       </c>
+      <c r="J43">
+        <v>2.56</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -2263,6 +2527,9 @@
       <c r="I44">
         <v>200</v>
       </c>
+      <c r="J44">
+        <v>2.85</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -2292,6 +2559,9 @@
       <c r="I45">
         <v>360</v>
       </c>
+      <c r="J45">
+        <v>2.85</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -2321,6 +2591,9 @@
       <c r="I46">
         <v>1010</v>
       </c>
+      <c r="J46">
+        <v>2.85</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -2350,6 +2623,9 @@
       <c r="I47">
         <v>360</v>
       </c>
+      <c r="J47">
+        <v>2.85</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -2379,6 +2655,9 @@
       <c r="I48">
         <v>200</v>
       </c>
+      <c r="J48">
+        <v>2.85</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -2408,6 +2687,9 @@
       <c r="I49">
         <v>1010</v>
       </c>
+      <c r="J49">
+        <v>2.85</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -2437,6 +2719,9 @@
       <c r="I50">
         <v>200</v>
       </c>
+      <c r="J50">
+        <v>2.85</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -2466,6 +2751,9 @@
       <c r="I51">
         <v>420</v>
       </c>
+      <c r="J51">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -2495,6 +2783,9 @@
       <c r="I52">
         <v>1140</v>
       </c>
+      <c r="J52">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -2524,6 +2815,9 @@
       <c r="I53">
         <v>230</v>
       </c>
+      <c r="J53">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -2553,6 +2847,9 @@
       <c r="I54">
         <v>1140</v>
       </c>
+      <c r="J54">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -2582,6 +2879,9 @@
       <c r="I55">
         <v>420</v>
       </c>
+      <c r="J55">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -2611,6 +2911,9 @@
       <c r="I56">
         <v>1140</v>
       </c>
+      <c r="J56">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -2640,6 +2943,9 @@
       <c r="I57">
         <v>230</v>
       </c>
+      <c r="J57">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -2669,6 +2975,9 @@
       <c r="I58">
         <v>805</v>
       </c>
+      <c r="J58">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -2698,6 +3007,9 @@
       <c r="I59">
         <v>405</v>
       </c>
+      <c r="J59">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -2727,6 +3039,9 @@
       <c r="I60">
         <v>2015</v>
       </c>
+      <c r="J60">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -2756,6 +3071,9 @@
       <c r="I61">
         <v>805</v>
       </c>
+      <c r="J61">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -2785,6 +3103,9 @@
       <c r="I62">
         <v>405</v>
       </c>
+      <c r="J62">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -2814,6 +3135,9 @@
       <c r="I63">
         <v>39000</v>
       </c>
+      <c r="J63">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -2843,17 +3167,20 @@
       <c r="I64">
         <v>405</v>
       </c>
+      <c r="J64">
+        <v>2.9</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J64"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2892,7 +3219,7 @@
         <v>charGrowth.expBase</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6">
@@ -2908,7 +3235,7 @@
         <v>charGrowth.statGrowthPerLevel</v>
       </c>
       <c r="B7">
-        <v>0.05</v>
+        <v>0.0338</v>
       </c>
     </row>
     <row r="8">
@@ -2916,60 +3243,92 @@
         <v>charGrowth.maxLevel</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>combat.minDamageRate</v>
+        <v>charGrowth.expSeg2Start</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>layout.frontMargin</v>
+        <v>charGrowth.expSeg2Growth</v>
       </c>
       <c r="B10">
-        <v>360</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>layout.spacing</v>
+        <v>charGrowth.expSeg3Start</v>
       </c>
       <c r="B11">
-        <v>110</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>bullet.speed</v>
+        <v>charGrowth.expSeg3Growth</v>
       </c>
       <c r="B12">
-        <v>1100</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>bullet.radius</v>
+        <v>combat.minDamageRate</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>layout.frontMargin</v>
+      </c>
+      <c r="B14">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>layout.spacing</v>
+      </c>
+      <c r="B15">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bullet.speed</v>
+      </c>
+      <c r="B16">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>bullet.radius</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>formation.contactGap</v>
       </c>
-      <c r="B14">
+      <c r="B18">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
   </ignoredErrors>
 </worksheet>
 </file>
